--- a/NECP Scenario/Results/Regional Results/KOS_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/KOS_Capacity.xlsx
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.304535941387898E-08</v>
+        <v>4.878584688174466E-08</v>
       </c>
       <c r="C3">
-        <v>3.322494450794876E-08</v>
+        <v>4.904993576379821E-08</v>
       </c>
       <c r="D3">
-        <v>0.0650458766056075</v>
+        <v>0.06504446348363729</v>
       </c>
       <c r="E3">
-        <v>0.08852517186083871</v>
+        <v>0.0885251665308564</v>
       </c>
       <c r="F3">
-        <v>0.1435792760280711</v>
+        <v>0.166985222350635</v>
       </c>
       <c r="G3">
-        <v>0.2765296536133343</v>
+        <v>0.2536785372047088</v>
       </c>
       <c r="H3">
-        <v>0.5757550808172947</v>
+        <v>0.5413642103002939</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.4000000000068355</v>
+        <v>0.4000000000073024</v>
       </c>
       <c r="C13">
-        <v>0.4000000000088814</v>
+        <v>0.4000000000103052</v>
       </c>
       <c r="D13">
-        <v>0.4000000000134354</v>
+        <v>0.4000000000161808</v>
       </c>
       <c r="E13">
-        <v>0.4000000000242666</v>
+        <v>0.4000000000291284</v>
       </c>
       <c r="F13">
-        <v>0.4000000000415263</v>
+        <v>0.4000000000516776</v>
       </c>
       <c r="G13">
-        <v>0.4000000000767455</v>
+        <v>0.4000000000942263</v>
       </c>
       <c r="H13">
-        <v>0.4000000004367375</v>
+        <v>0.4000000005235755</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1163,19 +1163,19 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0.2058214218224972</v>
+        <v>0.2058214217373747</v>
       </c>
       <c r="E27">
-        <v>0.2058214218956298</v>
+        <v>0.2058214218459345</v>
       </c>
       <c r="F27">
-        <v>0.2058214219276601</v>
+        <v>0.2058214218939761</v>
       </c>
       <c r="G27">
-        <v>0.2058214219520147</v>
+        <v>0.2058214219297811</v>
       </c>
       <c r="H27">
-        <v>0.2058214219771315</v>
+        <v>0.2058214219666075</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1215,19 +1215,19 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>1.207349757020208E-07</v>
+        <v>1.766515506417569E-07</v>
       </c>
       <c r="E29">
-        <v>0.0682541786096561</v>
+        <v>0.07109775222965881</v>
       </c>
       <c r="F29">
-        <v>0.09269427054675949</v>
+        <v>0.0926942704535592</v>
       </c>
       <c r="G29">
-        <v>0.0926942708124054</v>
+        <v>0.0926942707569216</v>
       </c>
       <c r="H29">
-        <v>0.0926942709203317</v>
+        <v>0.0926942708960078</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1319,19 +1319,19 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0.0519614983440306</v>
+        <v>0.0519614965413178</v>
       </c>
       <c r="E33">
-        <v>0.5726078671923147</v>
+        <v>0.5048209901438431</v>
       </c>
       <c r="F33">
-        <v>0.8217162929042873</v>
+        <v>0.7134671410139688</v>
       </c>
       <c r="G33">
-        <v>0.8217162944093709</v>
+        <v>0.713467142961814</v>
       </c>
       <c r="H33">
-        <v>1.148390502326654</v>
+        <v>1.022603111575026</v>
       </c>
     </row>
     <row r="34" spans="1:8">
